--- a/dashboard/ty_scan_cumulative.xlsx
+++ b/dashboard/ty_scan_cumulative.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>0528-1차</t>
   </si>
@@ -26,6 +26,15 @@
   </si>
   <si>
     <t>0529-1차</t>
+  </si>
+  <si>
+    <t>0529-2차</t>
+  </si>
+  <si>
+    <t>507146069195</t>
+  </si>
+  <si>
+    <t>507146069206</t>
   </si>
 </sst>
 </file>
@@ -357,10 +366,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -373,8 +382,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>302907583641</v>
       </c>
@@ -387,8 +399,11 @@
       <c r="D2">
         <v>302907392320</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>302907997002</v>
       </c>
@@ -401,8 +416,11 @@
       <c r="D3">
         <v>302907667545</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>302907698430</v>
       </c>
@@ -416,7 +434,7 @@
         <v>302907392515</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>302907661842</v>
       </c>
@@ -430,7 +448,7 @@
         <v>302908038420</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>302907194765</v>
       </c>
@@ -441,7 +459,7 @@
         <v>302907655472</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>302907849571</v>
       </c>
@@ -449,47 +467,47 @@
         <v>302907658585</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>302907734572</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>302907506545</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>302907416341</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>302907416444</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>302907497530</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>302907907520</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>302907189040</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>302907393112</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>302907584223</v>
       </c>

--- a/dashboard/ty_scan_cumulative.xlsx
+++ b/dashboard/ty_scan_cumulative.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>0528-1차</t>
   </si>
@@ -29,12 +29,6 @@
   </si>
   <si>
     <t>0529-2차</t>
-  </si>
-  <si>
-    <t>507146069195</t>
-  </si>
-  <si>
-    <t>507146069206</t>
   </si>
 </sst>
 </file>
@@ -399,8 +393,8 @@
       <c r="D2">
         <v>302907392320</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="E2">
+        <v>507146069195</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -416,8 +410,8 @@
       <c r="D3">
         <v>302907667545</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="E3">
+        <v>507146069206</v>
       </c>
     </row>
     <row r="4" spans="1:5">

--- a/dashboard/ty_scan_cumulative.xlsx
+++ b/dashboard/ty_scan_cumulative.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>0528-1차</t>
   </si>
@@ -29,6 +29,90 @@
   </si>
   <si>
     <t>0529-2차</t>
+  </si>
+  <si>
+    <t>0601-1차</t>
+  </si>
+  <si>
+    <t>0601-2차</t>
+  </si>
+  <si>
+    <t>0601-3차</t>
+  </si>
+  <si>
+    <t>0602-1차</t>
+  </si>
+  <si>
+    <t>0602-2차</t>
+  </si>
+  <si>
+    <t>302908024346</t>
+  </si>
+  <si>
+    <t>302908103181</t>
+  </si>
+  <si>
+    <t>302908149753</t>
+  </si>
+  <si>
+    <t>302907830855</t>
+  </si>
+  <si>
+    <t>302908235971</t>
+  </si>
+  <si>
+    <t>302907744372</t>
+  </si>
+  <si>
+    <t>302907506486</t>
+  </si>
+  <si>
+    <t>507145916993</t>
+  </si>
+  <si>
+    <t>507145916982</t>
+  </si>
+  <si>
+    <t>507145917004</t>
+  </si>
+  <si>
+    <t>301013399601</t>
+  </si>
+  <si>
+    <t>301013177513</t>
+  </si>
+  <si>
+    <t>302683765895</t>
+  </si>
+  <si>
+    <t>303511149084</t>
+  </si>
+  <si>
+    <t>303511149095</t>
+  </si>
+  <si>
+    <t>302683605470</t>
+  </si>
+  <si>
+    <t>302908103262</t>
+  </si>
+  <si>
+    <t>302908200385</t>
+  </si>
+  <si>
+    <t>302908128705</t>
+  </si>
+  <si>
+    <t>302908290232</t>
+  </si>
+  <si>
+    <t>303511560426</t>
+  </si>
+  <si>
+    <t>302908249046</t>
+  </si>
+  <si>
+    <t>302908224852</t>
   </si>
 </sst>
 </file>
@@ -360,10 +444,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -379,8 +463,23 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>302907583641</v>
       </c>
@@ -396,8 +495,23 @@
       <c r="E2">
         <v>507146069195</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>302907997002</v>
       </c>
@@ -413,8 +527,23 @@
       <c r="E3">
         <v>507146069206</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>302907698430</v>
       </c>
@@ -427,8 +556,17 @@
       <c r="D4">
         <v>302907392515</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>302907661842</v>
       </c>
@@ -441,8 +579,14 @@
       <c r="D5">
         <v>302908038420</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>302907194765</v>
       </c>
@@ -452,56 +596,80 @@
       <c r="D6">
         <v>302907655472</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>302907849571</v>
       </c>
       <c r="B7">
         <v>302907658585</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>302907734572</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>302907506545</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>302907416341</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>302907416444</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>302907497530</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>302907907520</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>302907189040</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>302907393112</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>302907584223</v>
       </c>

--- a/dashboard/ty_scan_cumulative.xlsx
+++ b/dashboard/ty_scan_cumulative.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>0528-1차</t>
   </si>
@@ -44,75 +44,6 @@
   </si>
   <si>
     <t>0602-2차</t>
-  </si>
-  <si>
-    <t>302908024346</t>
-  </si>
-  <si>
-    <t>302908103181</t>
-  </si>
-  <si>
-    <t>302908149753</t>
-  </si>
-  <si>
-    <t>302907830855</t>
-  </si>
-  <si>
-    <t>302908235971</t>
-  </si>
-  <si>
-    <t>302907744372</t>
-  </si>
-  <si>
-    <t>302907506486</t>
-  </si>
-  <si>
-    <t>507145916993</t>
-  </si>
-  <si>
-    <t>507145916982</t>
-  </si>
-  <si>
-    <t>507145917004</t>
-  </si>
-  <si>
-    <t>301013399601</t>
-  </si>
-  <si>
-    <t>301013177513</t>
-  </si>
-  <si>
-    <t>302683765895</t>
-  </si>
-  <si>
-    <t>303511149084</t>
-  </si>
-  <si>
-    <t>303511149095</t>
-  </si>
-  <si>
-    <t>302683605470</t>
-  </si>
-  <si>
-    <t>302908103262</t>
-  </si>
-  <si>
-    <t>302908200385</t>
-  </si>
-  <si>
-    <t>302908128705</t>
-  </si>
-  <si>
-    <t>302908290232</t>
-  </si>
-  <si>
-    <t>303511560426</t>
-  </si>
-  <si>
-    <t>302908249046</t>
-  </si>
-  <si>
-    <t>302908224852</t>
   </si>
 </sst>
 </file>
@@ -495,20 +426,20 @@
       <c r="E2">
         <v>507146069195</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
+      <c r="F2">
+        <v>302908024346</v>
+      </c>
+      <c r="G2">
+        <v>302683765895</v>
+      </c>
+      <c r="H2">
+        <v>302908103262</v>
+      </c>
+      <c r="I2">
+        <v>302908128705</v>
+      </c>
+      <c r="J2">
+        <v>303511560426</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -527,20 +458,20 @@
       <c r="E3">
         <v>507146069206</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
+      <c r="F3">
+        <v>302908103181</v>
+      </c>
+      <c r="G3">
+        <v>303511149084</v>
+      </c>
+      <c r="H3">
+        <v>302908200385</v>
+      </c>
+      <c r="I3">
+        <v>302908290232</v>
+      </c>
+      <c r="J3">
+        <v>302908249046</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -556,14 +487,14 @@
       <c r="D4">
         <v>302907392515</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
+      <c r="F4">
+        <v>302908149753</v>
+      </c>
+      <c r="G4">
+        <v>303511149095</v>
+      </c>
+      <c r="J4">
+        <v>302908224852</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -579,11 +510,11 @@
       <c r="D5">
         <v>302908038420</v>
       </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
+      <c r="F5">
+        <v>302907830855</v>
+      </c>
+      <c r="G5">
+        <v>302683605470</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -596,8 +527,8 @@
       <c r="D6">
         <v>302907655472</v>
       </c>
-      <c r="F6" t="s">
-        <v>14</v>
+      <c r="F6">
+        <v>302908235971</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -607,56 +538,56 @@
       <c r="B7">
         <v>302907658585</v>
       </c>
-      <c r="F7" t="s">
-        <v>15</v>
+      <c r="F7">
+        <v>302907744372</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
         <v>302907734572</v>
       </c>
-      <c r="F8" t="s">
-        <v>16</v>
+      <c r="F8">
+        <v>302907506486</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
         <v>302907506545</v>
       </c>
-      <c r="F9" t="s">
-        <v>17</v>
+      <c r="F9">
+        <v>507145916993</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
         <v>302907416341</v>
       </c>
-      <c r="F10" t="s">
-        <v>18</v>
+      <c r="F10">
+        <v>507145916982</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
         <v>302907416444</v>
       </c>
-      <c r="F11" t="s">
-        <v>19</v>
+      <c r="F11">
+        <v>507145917004</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
         <v>302907497530</v>
       </c>
-      <c r="F12" t="s">
-        <v>20</v>
+      <c r="F12">
+        <v>301013399601</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
         <v>302907907520</v>
       </c>
-      <c r="F13" t="s">
-        <v>21</v>
+      <c r="F13">
+        <v>301013177513</v>
       </c>
     </row>
     <row r="14" spans="1:10">
